--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260924.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260924.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -829,7 +829,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -959,7 +959,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11835,7 +11835,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14921,7 +14921,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15457,7 +15457,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -15993,7 +15993,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16395,7 +16395,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16797,7 +16797,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17199,7 +17199,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17333,7 +17333,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17668,7 +17668,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17802,7 +17802,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17869,7 +17869,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18271,7 +18271,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18405,7 +18405,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18472,7 +18472,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18539,7 +18539,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18740,7 +18740,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18874,7 +18874,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19075,7 +19075,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19142,7 +19142,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19343,7 +19343,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19410,7 +19410,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19477,7 +19477,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19745,7 +19745,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19812,7 +19812,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19879,7 +19879,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20013,7 +20013,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20147,7 +20147,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20214,7 +20214,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20281,7 +20281,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20415,7 +20415,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20482,7 +20482,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20616,7 +20616,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20817,7 +20817,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20884,7 +20884,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21018,7 +21018,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21085,7 +21085,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21152,7 +21152,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21286,7 +21286,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21420,7 +21420,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21487,7 +21487,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21554,7 +21554,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21621,7 +21621,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21688,7 +21688,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21822,7 +21822,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21889,7 +21889,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22090,7 +22090,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22157,7 +22157,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22224,7 +22224,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22425,7 +22425,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22492,7 +22492,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S327" s="1" t="n">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S328" s="1" t="n">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S329" s="1" t="n">
@@ -22693,7 +22693,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S330" s="1" t="n">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S331" s="1" t="n">
@@ -22811,7 +22811,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S332" t="inlineStr"/>
@@ -22860,7 +22860,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S333" t="inlineStr"/>
@@ -22909,7 +22909,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S334" t="inlineStr"/>
@@ -22958,7 +22958,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="S335" t="inlineStr"/>
